--- a/santi/科技.xlsx
+++ b/santi/科技.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ROG\Desktop\三体\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390D05A8-38CD-40E0-9A2E-53D35FDBC2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96550D4F-3D9B-49F8-B607-7B1D5A5B0E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="1484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="1476">
   <si>
     <t>名称</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -897,9 +897,6 @@
   <si>
     <t>return ctx.event === 'roll' &amp;&amp; ctx.consecutiveSameDisaster &gt;= 3;</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>新号别搞</t>
   </si>
   <si>
     <t>绝处逢生</t>
@@ -2848,10 +2845,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>降临</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>终结者</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3330,14 +3323,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>科学边界</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理学不存在了</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>return ctx.hasTech('量子力学');</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3773,10 +3758,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>雷德王</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>文明共同体</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3831,52 +3812,6 @@
     <t>文明观测到，希望之星被恒星吞噬，永远地消失了
 三体星系中只剩下了最后一颗行星
 获得难度：★★★</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>文明在第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>次观星时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>毁灭</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>return ctx.event === 'death' &amp;&amp; ctx.civilizationYears === 0;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -4579,10 +4514,6 @@
   </si>
   <si>
     <t>神们自己</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>永恒的终结</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -6873,7 +6804,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>76</v>
@@ -6905,13 +6836,13 @@
         <v>3</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>84</v>
@@ -6920,7 +6851,7 @@
         <v>85</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="116.5" customHeight="1">
@@ -6931,16 +6862,16 @@
         <v>3</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>80</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>85</v>
@@ -6954,19 +6885,19 @@
         <v>0</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>86</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="54" customHeight="1">
@@ -6977,30 +6908,30 @@
         <v>0</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>86</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="116.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B6" s="2">
         <v>3</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>11</v>
@@ -7023,25 +6954,25 @@
         <v>0</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>61</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>88</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="88.5" customHeight="1">
@@ -7052,59 +6983,59 @@
         <v>0</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>806</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>810</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>61</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>88</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="88.5" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B9" s="2">
         <v>0</v>
       </c>
       <c r="C9" s="15" t="s">
+        <v>650</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>651</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="88.5" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B10" s="2">
         <v>0</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="73" customHeight="1">
@@ -7115,45 +7046,45 @@
         <v>1</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>926</v>
+        <v>919</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="73" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="B12" s="2">
         <v>1</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>1299</v>
+        <v>1291</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>1314</v>
+        <v>1306</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>1364</v>
+        <v>1356</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>92</v>
@@ -7161,22 +7092,22 @@
     </row>
     <row r="13" spans="1:9" ht="73" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>1258</v>
+        <v>1250</v>
       </c>
       <c r="B13" s="2">
         <v>1</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>1259</v>
+        <v>1251</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1313</v>
+        <v>1305</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>1365</v>
+        <v>1357</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>92</v>
@@ -7184,254 +7115,254 @@
     </row>
     <row r="14" spans="1:9" ht="73" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>1261</v>
+        <v>1253</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>1263</v>
+        <v>1255</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>1262</v>
+        <v>1254</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>1366</v>
+        <v>1358</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>92</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="73" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>1260</v>
+        <v>1252</v>
       </c>
       <c r="B15" s="2">
         <v>1</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>1264</v>
+        <v>1256</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>1087</v>
+        <v>1079</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>1363</v>
+        <v>1355</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>1367</v>
+        <v>1359</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>92</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="86" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>1266</v>
+        <v>1258</v>
       </c>
       <c r="B16" s="2">
         <v>2</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>1268</v>
+        <v>1260</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>1269</v>
+        <v>1261</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>1309</v>
+        <v>1301</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>1311</v>
+        <v>1303</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>1312</v>
+        <v>1304</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>1293</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="73" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>1283</v>
+        <v>1275</v>
       </c>
       <c r="B17" s="2">
         <v>1</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>1280</v>
+        <v>1272</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>1288</v>
+        <v>1280</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>92</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>1294</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="73" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>1265</v>
+        <v>1257</v>
       </c>
       <c r="B18" s="2">
         <v>1</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1275</v>
+        <v>1267</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1270</v>
+        <v>1262</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>1271</v>
+        <v>1263</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>1289</v>
+        <v>1281</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>92</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>1295</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="93" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>1272</v>
+        <v>1264</v>
       </c>
       <c r="B19" s="2">
         <v>1</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1276</v>
+        <v>1268</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1273</v>
+        <v>1265</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>1285</v>
+        <v>1277</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>1290</v>
+        <v>1282</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>92</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>1296</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="93" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>1277</v>
+        <v>1269</v>
       </c>
       <c r="B20" s="2">
         <v>1</v>
       </c>
       <c r="C20" s="15" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>1278</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>1267</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>1286</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>1291</v>
+        <v>1283</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>92</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>1297</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="111.5" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="B21" s="2">
         <v>2</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>1282</v>
+        <v>1274</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1281</v>
+        <v>1273</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>1292</v>
+        <v>1284</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>92</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>1298</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="73" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B22" s="2">
         <v>0</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>1257</v>
+        <v>1249</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>61</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>88</v>
@@ -7439,22 +7370,22 @@
     </row>
     <row r="23" spans="1:9" ht="73" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B23" s="2">
         <v>0</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>61</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>88</v>
@@ -7468,16 +7399,16 @@
         <v>0</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>61</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>88</v>
@@ -7491,10 +7422,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>17</v>
@@ -7514,16 +7445,16 @@
         <v>0</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>1123</v>
+        <v>1115</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>65</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>88</v>
@@ -7537,22 +7468,22 @@
         <v>0</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>1124</v>
+        <v>1116</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>68</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>1125</v>
+        <v>1117</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="69" customHeight="1">
@@ -7563,16 +7494,16 @@
         <v>0</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>1126</v>
+        <v>1118</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>65</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>88</v>
@@ -7586,22 +7517,22 @@
         <v>0</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>1127</v>
+        <v>1119</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>65</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>1128</v>
+        <v>1120</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>88</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="94" customHeight="1">
@@ -7612,7 +7543,7 @@
         <v>0</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>29</v>
@@ -7641,10 +7572,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>22</v>
@@ -7659,7 +7590,7 @@
         <v>92</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="92" customHeight="1">
@@ -7670,10 +7601,10 @@
         <v>2</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>4</v>
@@ -7688,7 +7619,7 @@
         <v>90</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="64" customHeight="1">
@@ -7699,10 +7630,10 @@
         <v>0</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>36</v>
@@ -7714,10 +7645,10 @@
         <v>107</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="133.5" customHeight="1">
@@ -7728,10 +7659,10 @@
         <v>2</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>47</v>
@@ -7740,13 +7671,13 @@
         <v>5</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>90</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="88" customHeight="1">
@@ -7757,25 +7688,25 @@
         <v>1</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>43</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="89" customHeight="1">
@@ -7786,25 +7717,25 @@
         <v>2</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="F36" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>829</v>
+      </c>
+      <c r="H36" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="G36" s="5" t="s">
-        <v>833</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>361</v>
-      </c>
       <c r="I36" s="5" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="104.5" customHeight="1">
@@ -7815,13 +7746,13 @@
         <v>3</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>85</v>
@@ -7835,7 +7766,7 @@
         <v>0</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>16</v>
@@ -7858,19 +7789,19 @@
         <v>1</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>89</v>
@@ -7887,25 +7818,25 @@
         <v>3</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>51</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H40" s="5" t="s">
         <v>90</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="106" customHeight="1">
@@ -7916,25 +7847,25 @@
         <v>1</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H41" s="5" t="s">
         <v>89</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="105" customHeight="1">
@@ -7945,7 +7876,7 @@
         <v>2</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>49</v>
@@ -7963,7 +7894,7 @@
         <v>89</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="105" customHeight="1">
@@ -7974,25 +7905,25 @@
         <v>2</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>89</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="105" customHeight="1">
@@ -8003,25 +7934,25 @@
         <v>3</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>51</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>90</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="102.5" customHeight="1">
@@ -8032,10 +7963,10 @@
         <v>1</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>127</v>
@@ -8050,7 +7981,7 @@
         <v>96</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="112" customHeight="1">
@@ -8061,25 +7992,25 @@
         <v>2</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>1161</v>
+        <v>1153</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>24</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>1162</v>
+        <v>1154</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>97</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="64" customHeight="1">
@@ -8090,16 +8021,16 @@
         <v>0</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>40</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>98</v>
@@ -8113,7 +8044,7 @@
         <v>0</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>42</v>
@@ -8142,25 +8073,25 @@
         <v>0</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>1152</v>
+        <v>1144</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>1153</v>
+        <v>1145</v>
       </c>
       <c r="H49" s="5" t="s">
         <v>102</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="105.5" customHeight="1">
@@ -8171,25 +8102,25 @@
         <v>1</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="94" customHeight="1">
@@ -8200,16 +8131,16 @@
         <v>2</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>89</v>
@@ -8223,16 +8154,16 @@
         <v>0</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="H52" s="5" t="s">
         <v>89</v>
@@ -8246,13 +8177,13 @@
         <v>0</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E53" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="G53" s="5" t="s">
         <v>364</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>365</v>
       </c>
       <c r="H53" s="5" t="s">
         <v>85</v>
@@ -8260,22 +8191,22 @@
     </row>
     <row r="54" spans="1:9" ht="63.5" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B54" s="2">
         <v>0</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>65</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H54" s="5" t="s">
         <v>88</v>
@@ -8289,19 +8220,19 @@
         <v>0</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>65</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H55" s="5" t="s">
         <v>88</v>
@@ -8312,31 +8243,31 @@
     </row>
     <row r="56" spans="1:9" ht="98" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B56" s="2">
         <v>1</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>1154</v>
+        <v>1146</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>1155</v>
+        <v>1147</v>
       </c>
       <c r="H56" s="5" t="s">
         <v>102</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="107.5" customHeight="1">
@@ -8347,10 +8278,10 @@
         <v>0</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>60</v>
@@ -8365,7 +8296,7 @@
         <v>89</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="108.5" customHeight="1">
@@ -8376,16 +8307,16 @@
         <v>1</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>40</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>98</v>
@@ -8399,16 +8330,16 @@
         <v>0</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>89</v>
@@ -8422,25 +8353,25 @@
         <v>2</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="H60" s="5" t="s">
         <v>102</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="104" customHeight="1">
@@ -8451,19 +8382,19 @@
         <v>1</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>1122</v>
+        <v>1114</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>1121</v>
+        <v>1113</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="98.5" customHeight="1">
@@ -8474,7 +8405,7 @@
         <v>1</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>109</v>
@@ -8483,13 +8414,13 @@
         <v>110</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>119</v>
@@ -8503,25 +8434,25 @@
         <v>1</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>131</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>132</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="84" customHeight="1">
@@ -8532,25 +8463,25 @@
         <v>1</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>114</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>120</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="103" customHeight="1">
@@ -8561,83 +8492,83 @@
         <v>1</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>116</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="91" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B66" s="2">
         <v>1</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>117</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="118.5" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B67" s="2">
         <v>1</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>65</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H67" s="5" t="s">
         <v>88</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="97.5" customHeight="1">
@@ -8648,25 +8579,25 @@
         <v>0</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>121</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>65</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="93.5" customHeight="1">
@@ -8677,16 +8608,16 @@
         <v>3</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>128</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="H69" s="5" t="s">
         <v>130</v>
@@ -8700,16 +8631,16 @@
         <v>3</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>129</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="H70" s="5" t="s">
         <v>130</v>
@@ -8723,10 +8654,10 @@
         <v>2</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>123</v>
@@ -8735,1576 +8666,1576 @@
         <v>17</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="H71" s="5" t="s">
         <v>89</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="64" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B72" s="2">
         <v>0</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G72" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="H72" s="5" t="s">
         <v>452</v>
-      </c>
-      <c r="H72" s="5" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="70.5" customHeight="1">
       <c r="A73" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B73" s="2">
+        <v>1</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>1122</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="I73" s="5" t="s">
         <v>491</v>
-      </c>
-      <c r="B73" s="2">
-        <v>1</v>
-      </c>
-      <c r="C73" s="15" t="s">
-        <v>1131</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>861</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>1129</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="G73" s="5" t="s">
-        <v>1130</v>
-      </c>
-      <c r="H73" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="I73" s="5" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="73.5" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B74" s="2">
         <v>0</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="64" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B75" s="2">
         <v>0</v>
       </c>
       <c r="C75" s="15" t="s">
+        <v>575</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>576</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>577</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>111</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H75" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="I75" s="5" t="s">
         <v>455</v>
-      </c>
-      <c r="I75" s="5" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="79.5" customHeight="1">
       <c r="A76" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B76" s="2">
+        <v>1</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>578</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="B76" s="2">
-        <v>1</v>
-      </c>
-      <c r="C76" s="15" t="s">
-        <v>579</v>
-      </c>
-      <c r="D76" s="3" t="s">
+      <c r="F76" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="H76" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="I76" s="5" t="s">
         <v>623</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="G76" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="H76" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="I76" s="5" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="110" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B77" s="2">
         <v>2</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>1132</v>
+        <v>1124</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>1133</v>
+        <v>1125</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="64" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B78" s="2">
         <v>0</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="90.5" customHeight="1">
       <c r="A79" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B79" s="2">
+        <v>1</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>579</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="B79" s="2">
-        <v>1</v>
-      </c>
-      <c r="C79" s="15" t="s">
-        <v>580</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>398</v>
-      </c>
       <c r="F79" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="93" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B80" s="2">
         <v>2</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="E80" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="G80" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="F80" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="G80" s="5" t="s">
-        <v>582</v>
-      </c>
       <c r="H80" s="5" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="84" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B81" s="2">
         <v>2</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="86.5" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B82" s="2">
         <v>0</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F82" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H82" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="G82" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="H82" s="5" t="s">
-        <v>460</v>
-      </c>
       <c r="I82" s="5" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="78" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B83" s="2">
         <v>0</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F83" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="H83" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="G83" s="5" t="s">
+      <c r="I83" s="5" t="s">
         <v>465</v>
-      </c>
-      <c r="H83" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="I83" s="5" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="64" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B84" s="2">
         <v>1</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>1134</v>
+        <v>1126</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>1135</v>
+        <v>1127</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="64" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B85" s="2">
         <v>3</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>1106</v>
+        <v>1098</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>1104</v>
+        <v>1096</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>1105</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="64" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B86" s="2">
         <v>1</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="64" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B87" s="2">
         <v>1</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="90" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B88" s="2">
         <v>2</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>1136</v>
+        <v>1128</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>1137</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="64" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B89" s="2">
         <v>2</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="64" customHeight="1">
       <c r="A90" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B90" s="2">
         <v>2</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>1060</v>
+        <v>1052</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="64" customHeight="1">
       <c r="A91" s="2" t="s">
-        <v>1061</v>
+        <v>1053</v>
       </c>
       <c r="B91" s="2">
         <v>2</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>1062</v>
+        <v>1054</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>1063</v>
+        <v>1055</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>1064</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="64" customHeight="1">
       <c r="A92" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B92" s="2">
         <v>2</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="64" customHeight="1">
       <c r="A93" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B93" s="2">
         <v>2</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="64" customHeight="1">
       <c r="A94" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B94" s="2">
         <v>2</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="64" customHeight="1">
       <c r="A95" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B95" s="2">
         <v>2</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="64" customHeight="1">
       <c r="A96" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B96" s="2">
         <v>2</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="64" customHeight="1">
       <c r="A97" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B97" s="2">
         <v>1</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>1194</v>
+        <v>1186</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>1195</v>
+        <v>1187</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I97" s="5" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="95.5" customHeight="1">
       <c r="A98" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B98" s="2">
         <v>1</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D98" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="E98" s="3" t="s">
         <v>428</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>429</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="94.5" customHeight="1">
       <c r="A99" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B99" s="2">
         <v>2</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>1201</v>
+        <v>1193</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>1203</v>
+        <v>1195</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>1204</v>
+        <v>1196</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>1202</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="102" customHeight="1">
       <c r="A100" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B100" s="2">
         <v>3</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="102" customHeight="1">
       <c r="A101" s="2" t="s">
-        <v>1200</v>
+        <v>1192</v>
       </c>
       <c r="B101" s="2">
         <v>1</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>1205</v>
+        <v>1197</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>1207</v>
+        <v>1199</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="102" customHeight="1">
       <c r="A102" s="2" t="s">
-        <v>1206</v>
+        <v>1198</v>
       </c>
       <c r="B102" s="2">
         <v>1</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>1209</v>
+        <v>1201</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>1208</v>
+        <v>1200</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>1235</v>
+        <v>1227</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="102" customHeight="1">
       <c r="A103" s="2" t="s">
-        <v>1210</v>
+        <v>1202</v>
       </c>
       <c r="B103" s="2">
         <v>2</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>1213</v>
+        <v>1205</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>1087</v>
+        <v>1079</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>1211</v>
+        <v>1203</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>1212</v>
+        <v>1204</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>1236</v>
+        <v>1228</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>1240</v>
+        <v>1232</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="102" customHeight="1">
       <c r="A104" s="2" t="s">
-        <v>1214</v>
+        <v>1206</v>
       </c>
       <c r="B104" s="2">
         <v>1</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>1215</v>
+        <v>1207</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>1211</v>
+        <v>1203</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>1212</v>
+        <v>1204</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>1236</v>
+        <v>1228</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>1240</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="102" customHeight="1">
       <c r="A105" s="2" t="s">
-        <v>1216</v>
+        <v>1208</v>
       </c>
       <c r="B105" s="2">
         <v>2</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>1218</v>
+        <v>1210</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>1089</v>
+        <v>1081</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>1217</v>
+        <v>1209</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>1212</v>
+        <v>1204</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>1240</v>
+        <v>1232</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="247.5" customHeight="1">
       <c r="A106" s="2" t="s">
-        <v>1219</v>
+        <v>1211</v>
       </c>
       <c r="B106" s="2">
         <v>2</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>1221</v>
+        <v>1213</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>1087</v>
+        <v>1079</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>1220</v>
+        <v>1212</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>1212</v>
+        <v>1204</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>1433</v>
+        <v>1425</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>1240</v>
+        <v>1232</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="102" customHeight="1">
       <c r="A107" s="2" t="s">
-        <v>1222</v>
+        <v>1214</v>
       </c>
       <c r="B107" s="2">
         <v>1</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>1225</v>
+        <v>1217</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>1300</v>
+        <v>1292</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>1301</v>
+        <v>1293</v>
       </c>
       <c r="H107" s="5" t="s">
         <v>92</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="102" customHeight="1">
       <c r="A108" s="2" t="s">
-        <v>1223</v>
+        <v>1215</v>
       </c>
       <c r="B108" s="2">
         <v>3</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>1224</v>
+        <v>1216</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>1230</v>
+        <v>1222</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>1471</v>
+        <v>1463</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>1472</v>
+        <v>1464</v>
       </c>
       <c r="H108" s="5" t="s">
         <v>92</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>1241</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="102" customHeight="1">
       <c r="A109" s="2" t="s">
-        <v>1226</v>
+        <v>1218</v>
       </c>
       <c r="B109" s="2">
         <v>2</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>1229</v>
+        <v>1221</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>1227</v>
+        <v>1219</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>1228</v>
+        <v>1220</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>1238</v>
+        <v>1230</v>
       </c>
       <c r="H109" s="5" t="s">
         <v>92</v>
       </c>
       <c r="I109" s="5" t="s">
-        <v>1242</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="102" customHeight="1">
       <c r="A110" s="2" t="s">
-        <v>1231</v>
+        <v>1223</v>
       </c>
       <c r="B110" s="2">
         <v>2</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>1233</v>
+        <v>1225</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>968</v>
+        <v>961</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>1232</v>
+        <v>1224</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>1239</v>
+        <v>1231</v>
       </c>
       <c r="H110" s="5" t="s">
         <v>92</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>1243</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="64" customHeight="1">
       <c r="A111" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B111" s="2">
         <v>1</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>1138</v>
+        <v>1130</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="92.5" customHeight="1">
       <c r="A112" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B112" s="2">
         <v>0</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G112" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="H112" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="H112" s="5" t="s">
-        <v>479</v>
-      </c>
       <c r="I112" s="5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="64" customHeight="1">
       <c r="A113" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B113" s="2">
         <v>1</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>1140</v>
+        <v>1132</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>1141</v>
+        <v>1133</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="100" customHeight="1">
       <c r="A114" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B114" s="2">
         <v>2</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>1099</v>
+        <v>1091</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>1142</v>
+        <v>1134</v>
       </c>
       <c r="F114" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>1135</v>
+      </c>
+      <c r="H114" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="G114" s="5" t="s">
-        <v>1143</v>
-      </c>
-      <c r="H114" s="5" t="s">
-        <v>519</v>
-      </c>
       <c r="I114" s="5" t="s">
-        <v>1100</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="72.5" customHeight="1">
       <c r="A115" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B115" s="2">
         <v>1</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>1142</v>
+        <v>1134</v>
       </c>
       <c r="F115" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>1135</v>
+      </c>
+      <c r="H115" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="G115" s="5" t="s">
-        <v>1143</v>
-      </c>
-      <c r="H115" s="5" t="s">
-        <v>519</v>
-      </c>
       <c r="I115" s="5" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="85.5" customHeight="1">
       <c r="A116" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B116" s="2">
         <v>0</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>1144</v>
+        <v>1136</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>1145</v>
+        <v>1137</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="85.5" customHeight="1">
       <c r="A117" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B117" s="2">
+        <v>1</v>
+      </c>
+      <c r="C117" s="15" t="s">
+        <v>601</v>
+      </c>
+      <c r="D117" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="B117" s="2">
-        <v>1</v>
-      </c>
-      <c r="C117" s="15" t="s">
-        <v>602</v>
-      </c>
-      <c r="D117" s="3" t="s">
+      <c r="E117" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F117" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="E117" s="3" t="s">
-        <v>1146</v>
-      </c>
-      <c r="F117" s="3" t="s">
-        <v>496</v>
-      </c>
       <c r="G117" s="5" t="s">
-        <v>1147</v>
+        <v>1139</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I117" s="5" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="108" customHeight="1">
       <c r="A118" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B118" s="2">
         <v>1</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>1192</v>
+        <v>1184</v>
       </c>
       <c r="F118" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>1185</v>
+      </c>
+      <c r="H118" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="G118" s="5" t="s">
-        <v>1193</v>
-      </c>
-      <c r="H118" s="5" t="s">
-        <v>519</v>
-      </c>
       <c r="I118" s="5" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="100" customHeight="1">
       <c r="A119" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B119" s="2">
         <v>1</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D119" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F119" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="E119" s="3" t="s">
-        <v>1190</v>
-      </c>
-      <c r="F119" s="3" t="s">
-        <v>500</v>
-      </c>
       <c r="G119" s="5" t="s">
-        <v>1191</v>
+        <v>1183</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I119" s="5" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="81" customHeight="1">
       <c r="A120" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B120" s="2">
         <v>0</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I120" s="5" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="64" customHeight="1">
       <c r="A121" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B121" s="2">
         <v>0</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>1370</v>
+        <v>1362</v>
       </c>
       <c r="F121" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="G121" s="5" t="s">
+        <v>1363</v>
+      </c>
+      <c r="H121" s="5" t="s">
         <v>518</v>
-      </c>
-      <c r="G121" s="5" t="s">
-        <v>1371</v>
-      </c>
-      <c r="H121" s="5" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="87.5" customHeight="1">
       <c r="A122" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B122" s="2">
         <v>0</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>1437</v>
+        <v>1429</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="107" customHeight="1">
       <c r="A123" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B123" s="2">
         <v>1</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>1186</v>
+        <v>1178</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>1187</v>
+        <v>1179</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="85" customHeight="1">
       <c r="A124" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B124" s="2">
         <v>2</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>1188</v>
+        <v>1180</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>1189</v>
+        <v>1181</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I124" s="5" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="89.5" customHeight="1">
       <c r="A125" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B125" s="2">
         <v>2</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>1089</v>
+        <v>1081</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>1372</v>
+        <v>1364</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>1373</v>
+        <v>1365</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I125" s="5" t="s">
-        <v>1097</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="64" customHeight="1">
       <c r="A126" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B126" s="2">
         <v>0</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>1368</v>
+        <v>1360</v>
       </c>
       <c r="F126" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="G126" s="5" t="s">
+        <v>1361</v>
+      </c>
+      <c r="H126" s="5" t="s">
         <v>518</v>
-      </c>
-      <c r="G126" s="5" t="s">
-        <v>1369</v>
-      </c>
-      <c r="H126" s="5" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="81" customHeight="1">
       <c r="A127" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B127" s="2">
         <v>1</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>1375</v>
+        <v>1367</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="99" customHeight="1">
       <c r="A128" s="2" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B128" s="2">
         <v>1</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>1374</v>
+        <v>1366</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>1377</v>
+        <v>1369</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="74.5" customHeight="1">
       <c r="A129" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B129" s="2">
         <v>1</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>1184</v>
+        <v>1176</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>1185</v>
+        <v>1177</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="89.5" customHeight="1">
       <c r="A130" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B130" s="2">
         <v>1</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>1107</v>
+        <v>1099</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>1108</v>
+        <v>1100</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="I130" s="5" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="70.5" customHeight="1">
       <c r="A131" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B131" s="2">
         <v>2</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>1196</v>
+        <v>1188</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>1197</v>
+        <v>1189</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="104.5" customHeight="1">
       <c r="A132" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B132" s="2">
         <v>2</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>1098</v>
+        <v>1090</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>1198</v>
+        <v>1190</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>1199</v>
+        <v>1191</v>
       </c>
       <c r="H132" s="5" t="s">
         <v>92</v>
       </c>
       <c r="I132" s="5" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="75" customHeight="1">
       <c r="A133" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B133" s="2">
+        <v>1</v>
+      </c>
+      <c r="C133" s="15" t="s">
+        <v>729</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="E133" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="B133" s="2">
-        <v>1</v>
-      </c>
-      <c r="C133" s="15" t="s">
-        <v>731</v>
-      </c>
-      <c r="D133" s="3" t="s">
-        <v>726</v>
-      </c>
-      <c r="E133" s="3" t="s">
-        <v>727</v>
-      </c>
       <c r="F133" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="I133" s="5" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="75.5" customHeight="1">
       <c r="A134" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="B134" s="2">
+        <v>1</v>
+      </c>
+      <c r="C134" s="15" t="s">
         <v>728</v>
       </c>
-      <c r="B134" s="2">
-        <v>1</v>
-      </c>
-      <c r="C134" s="15" t="s">
-        <v>730</v>
-      </c>
       <c r="E134" s="3" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="H134" s="5" t="s">
         <v>92</v>
@@ -10312,488 +10243,488 @@
     </row>
     <row r="135" spans="1:9" ht="64" customHeight="1">
       <c r="A135" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B135" s="2">
         <v>1</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>1182</v>
+        <v>1174</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>1183</v>
+        <v>1175</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="82.5" customHeight="1">
       <c r="A136" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B136" s="2">
         <v>2</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>1089</v>
+        <v>1081</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>1378</v>
+        <v>1370</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>1379</v>
+        <v>1371</v>
       </c>
       <c r="H136" s="5" t="s">
         <v>92</v>
       </c>
       <c r="I136" s="5" t="s">
-        <v>1097</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="85.5" customHeight="1">
       <c r="A137" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="B137" s="2">
+        <v>1</v>
+      </c>
+      <c r="C137" s="15" t="s">
         <v>738</v>
       </c>
-      <c r="B137" s="2">
-        <v>1</v>
-      </c>
-      <c r="C137" s="15" t="s">
-        <v>740</v>
-      </c>
       <c r="D137" s="3" t="s">
-        <v>1087</v>
+        <v>1079</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="I137" s="5" t="s">
-        <v>1096</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="80" customHeight="1">
       <c r="A138" s="2" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B138" s="2">
         <v>1</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>1380</v>
+        <v>1372</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>1381</v>
+        <v>1373</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="85.5" customHeight="1">
       <c r="A139" s="2" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B139" s="2">
         <v>1</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>1465</v>
+        <v>1457</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>1466</v>
+        <v>1458</v>
       </c>
       <c r="H139" s="5" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="85.5" customHeight="1">
       <c r="A140" s="2" t="s">
-        <v>949</v>
+        <v>942</v>
       </c>
       <c r="B140" s="2">
         <v>1</v>
       </c>
       <c r="C140" s="15" t="s">
-        <v>951</v>
+        <v>944</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>1465</v>
+        <v>1457</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>1466</v>
+        <v>1458</v>
       </c>
       <c r="H140" s="5" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="80" customHeight="1">
       <c r="A141" s="2" t="s">
-        <v>950</v>
+        <v>943</v>
       </c>
       <c r="B141" s="2">
         <v>2</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>1467</v>
+        <v>1459</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>1468</v>
+        <v>1460</v>
       </c>
       <c r="H141" s="5" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="90" customHeight="1">
       <c r="A142" s="2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B142" s="2">
         <v>2</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>1473</v>
+        <v>1465</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>1474</v>
+        <v>1466</v>
       </c>
       <c r="H142" s="5" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="109.5" customHeight="1">
       <c r="A143" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B143" s="2">
         <v>2</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>1469</v>
+        <v>1461</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>1470</v>
+        <v>1462</v>
       </c>
       <c r="H143" s="5" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="109.5" customHeight="1">
       <c r="A144" s="2" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="B144" s="2">
         <v>2</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>1382</v>
+        <v>1374</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>1384</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="109.5" customHeight="1">
       <c r="A145" s="2" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="B145" s="2">
         <v>2</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>1383</v>
+        <v>1375</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>1385</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="109.5" customHeight="1">
       <c r="A146" s="2" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="B146" s="2">
         <v>3</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>1386</v>
+        <v>1378</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>1387</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="121.5" customHeight="1">
       <c r="A147" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B147" s="2">
         <v>1</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>1388</v>
+        <v>1380</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>1389</v>
+        <v>1381</v>
       </c>
       <c r="H147" s="5" t="s">
-        <v>1033</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="94" customHeight="1">
       <c r="A148" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B148" s="2">
         <v>1</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>1390</v>
+        <v>1382</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>1391</v>
+        <v>1383</v>
       </c>
       <c r="H148" s="5" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="I148" s="5" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="94" customHeight="1">
       <c r="A149" s="2" t="s">
-        <v>958</v>
+        <v>951</v>
       </c>
       <c r="B149" s="2">
         <v>2</v>
       </c>
       <c r="C149" s="15" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>1030</v>
+        <v>1023</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>1166</v>
+        <v>1158</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>1167</v>
+        <v>1159</v>
       </c>
       <c r="H149" s="5" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="I149" s="5" t="s">
-        <v>1092</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="109.5" customHeight="1">
       <c r="A150" s="2" t="s">
-        <v>952</v>
+        <v>945</v>
       </c>
       <c r="B150" s="2">
         <v>1</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>953</v>
+        <v>946</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>1477</v>
+        <v>1469</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="H150" s="5" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="109.5" customHeight="1">
       <c r="A151" s="2" t="s">
-        <v>954</v>
+        <v>947</v>
       </c>
       <c r="B151" s="2">
         <v>3</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>956</v>
+        <v>949</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>955</v>
+        <v>948</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>1392</v>
+        <v>1384</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>1393</v>
+        <v>1385</v>
       </c>
       <c r="H151" s="5" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="109.5" customHeight="1">
       <c r="A152" s="2" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="B152" s="2">
         <v>2</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>961</v>
+        <v>954</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>1394</v>
+        <v>1386</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>1395</v>
+        <v>1387</v>
       </c>
       <c r="H152" s="5" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="88" customHeight="1">
       <c r="A153" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B153" s="2">
         <v>3</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>957</v>
+        <v>950</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>1396</v>
+        <v>1388</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>1397</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="88" customHeight="1">
       <c r="A154" s="2" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="B154" s="2">
         <v>1</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>1398</v>
+        <v>1390</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>1399</v>
+        <v>1391</v>
       </c>
       <c r="H154" s="5" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="88" customHeight="1">
       <c r="A155" s="2" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="B155" s="2">
         <v>1</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>1400</v>
+        <v>1392</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>1401</v>
+        <v>1393</v>
       </c>
       <c r="H155" s="5" t="s">
         <v>92</v>
@@ -10801,74 +10732,74 @@
     </row>
     <row r="156" spans="1:9" ht="88" customHeight="1">
       <c r="A156" s="2" t="s">
-        <v>989</v>
+        <v>982</v>
       </c>
       <c r="B156" s="2">
         <v>2</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>968</v>
+        <v>961</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>1402</v>
+        <v>1394</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>1403</v>
+        <v>1395</v>
       </c>
       <c r="H156" s="5" t="s">
         <v>92</v>
       </c>
       <c r="I156" s="5" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="109.5" customHeight="1">
       <c r="A157" s="2" t="s">
-        <v>965</v>
+        <v>958</v>
       </c>
       <c r="B157" s="2">
         <v>2</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>966</v>
+        <v>959</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>1148</v>
+        <v>1140</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>1149</v>
+        <v>1141</v>
       </c>
       <c r="H157" s="5" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="109.5" customHeight="1">
       <c r="A158" s="2" t="s">
-        <v>978</v>
+        <v>971</v>
       </c>
       <c r="B158" s="2">
         <v>1</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>979</v>
+        <v>972</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>1404</v>
+        <v>1396</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="H158" s="5" t="s">
         <v>92</v>
@@ -10876,91 +10807,91 @@
     </row>
     <row r="159" spans="1:9" ht="109.5" customHeight="1">
       <c r="A159" s="2" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
       <c r="B159" s="2">
         <v>1</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>967</v>
+        <v>960</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>1406</v>
+        <v>1398</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>1407</v>
+        <v>1399</v>
       </c>
       <c r="H159" s="5" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="109.5" customHeight="1">
       <c r="A160" s="2" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="B160" s="2">
         <v>1</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>1019</v>
+        <v>1012</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>1408</v>
+        <v>1400</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>1409</v>
+        <v>1401</v>
       </c>
       <c r="H160" s="5" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="109.5" customHeight="1">
       <c r="A161" s="2" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="B161" s="2">
         <v>1</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>963</v>
+        <v>956</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>1168</v>
+        <v>1160</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>1169</v>
+        <v>1161</v>
       </c>
       <c r="H161" s="5" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="109.5" customHeight="1">
       <c r="A162" s="2" t="s">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="B162" s="2">
         <v>1</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>1410</v>
+        <v>1402</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="H162" s="5" t="s">
         <v>92</v>
@@ -10968,299 +10899,299 @@
     </row>
     <row r="163" spans="1:9" ht="80.5" customHeight="1">
       <c r="A163" s="2" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="B163" s="2">
         <v>2</v>
       </c>
       <c r="C163" s="15" t="s">
+        <v>963</v>
+      </c>
+      <c r="E163" s="3" t="s">
         <v>970</v>
-      </c>
-      <c r="E163" s="3" t="s">
-        <v>977</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
       <c r="H163" s="5" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="108.5" customHeight="1">
       <c r="A164" s="2" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="B164" s="2">
         <v>1</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>1087</v>
+        <v>1079</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>1170</v>
+        <v>1162</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>1171</v>
+        <v>1163</v>
       </c>
       <c r="H164" s="5" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
       <c r="I164" s="5" t="s">
-        <v>1093</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="98" customHeight="1">
       <c r="A165" s="2" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B165" s="2">
         <v>2</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>986</v>
+        <v>979</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>1083</v>
+        <v>1075</v>
       </c>
       <c r="H165" s="5" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="I165" s="5" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="94.5" customHeight="1">
       <c r="A166" s="2" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="B166" s="2">
         <v>2</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>1413</v>
+        <v>1405</v>
       </c>
       <c r="H166" s="5" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="94.5" customHeight="1">
       <c r="A167" s="2" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
       <c r="B167" s="2">
         <v>1</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>1172</v>
+        <v>1164</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>1173</v>
+        <v>1165</v>
       </c>
       <c r="H167" s="5" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="108.5" customHeight="1">
       <c r="A168" s="2" t="s">
-        <v>993</v>
+        <v>986</v>
       </c>
       <c r="B168" s="2">
         <v>2</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>1109</v>
+        <v>1101</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>1110</v>
+        <v>1102</v>
       </c>
       <c r="H168" s="5" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="95.5" customHeight="1">
       <c r="A169" s="2" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="B169" s="2">
         <v>2</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>1089</v>
+        <v>1081</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>1174</v>
+        <v>1166</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>1175</v>
+        <v>1167</v>
       </c>
       <c r="H169" s="5" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="I169" s="5" t="s">
-        <v>1094</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="93.5" customHeight="1">
       <c r="A170" s="2" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="B170" s="2">
         <v>1</v>
       </c>
       <c r="C170" s="15" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="H170" s="5" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I170" s="5" t="s">
         <v>1035</v>
-      </c>
-      <c r="I170" s="5" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="171" spans="1:9" ht="86.5" customHeight="1">
       <c r="A171" s="2" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="B171" s="2">
         <v>1</v>
       </c>
       <c r="C171" s="15" t="s">
-        <v>1001</v>
+        <v>994</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>1150</v>
+        <v>1142</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="H171" s="5" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="86.5" customHeight="1">
       <c r="A172" s="2" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="B172" s="2">
         <v>2</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="G172" s="5" t="s">
-        <v>1041</v>
+        <v>1034</v>
       </c>
       <c r="H172" s="5" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="84" customHeight="1">
       <c r="A173" s="2" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="B173" s="2">
         <v>2</v>
       </c>
       <c r="C173" s="15" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>1414</v>
+        <v>1406</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>1416</v>
+        <v>1408</v>
       </c>
       <c r="H173" s="5" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="75" customHeight="1">
       <c r="A174" s="2" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="B174" s="2">
         <v>2</v>
       </c>
       <c r="C174" s="15" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>1415</v>
+        <v>1407</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>1417</v>
+        <v>1409</v>
       </c>
       <c r="H174" s="5" t="s">
         <v>92</v>
@@ -11268,523 +11199,523 @@
     </row>
     <row r="175" spans="1:9" ht="64" customHeight="1">
       <c r="A175" s="2" t="s">
-        <v>1020</v>
+        <v>1013</v>
       </c>
       <c r="B175" s="2">
         <v>1</v>
       </c>
       <c r="C175" s="15" t="s">
-        <v>1021</v>
+        <v>1014</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>1418</v>
+        <v>1410</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>1113</v>
+        <v>1105</v>
       </c>
       <c r="H175" s="5" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="83.5" customHeight="1">
       <c r="A176" s="2" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="B176" s="2">
         <v>2</v>
       </c>
       <c r="C176" s="15" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>1176</v>
+        <v>1168</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>1177</v>
+        <v>1169</v>
       </c>
       <c r="H176" s="5" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="92.5" customHeight="1">
       <c r="A177" s="2" t="s">
-        <v>1023</v>
+        <v>1016</v>
       </c>
       <c r="B177" s="2">
         <v>3</v>
       </c>
       <c r="C177" s="15" t="s">
-        <v>1022</v>
+        <v>1015</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>1419</v>
+        <v>1411</v>
       </c>
       <c r="G177" s="5" t="s">
-        <v>1420</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="178" spans="1:9" ht="83.5" customHeight="1">
       <c r="A178" s="2" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
       <c r="B178" s="2">
         <v>1</v>
       </c>
       <c r="C178" s="15" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="D178" s="3" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="G178" s="5" t="s">
+        <v>1171</v>
+      </c>
+      <c r="H178" s="5" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I178" s="5" t="s">
         <v>1087</v>
-      </c>
-      <c r="E178" s="3" t="s">
-        <v>1178</v>
-      </c>
-      <c r="F178" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="G178" s="5" t="s">
-        <v>1179</v>
-      </c>
-      <c r="H178" s="5" t="s">
-        <v>1035</v>
-      </c>
-      <c r="I178" s="5" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="179" spans="1:9" ht="84" customHeight="1">
       <c r="A179" s="2" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
       <c r="B179" s="2">
         <v>2</v>
       </c>
       <c r="C179" s="15" t="s">
-        <v>1088</v>
+        <v>1080</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>1180</v>
+        <v>1172</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>1181</v>
+        <v>1173</v>
       </c>
       <c r="H179" s="5" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="I179" s="5" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="180" spans="1:9" ht="83.5" customHeight="1">
       <c r="A180" s="2" t="s">
-        <v>1031</v>
+        <v>1024</v>
       </c>
       <c r="B180" s="2">
         <v>2</v>
       </c>
       <c r="C180" s="15" t="s">
-        <v>1032</v>
+        <v>1025</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>1421</v>
+        <v>1413</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
       <c r="G180" s="5" t="s">
-        <v>1422</v>
+        <v>1414</v>
       </c>
       <c r="H180" s="5" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="181" spans="1:9" ht="107.5" customHeight="1">
       <c r="A181" s="2" t="s">
-        <v>1024</v>
+        <v>1017</v>
       </c>
       <c r="B181" s="2">
         <v>3</v>
       </c>
       <c r="C181" s="15" t="s">
-        <v>1026</v>
+        <v>1019</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>1423</v>
+        <v>1415</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>1424</v>
+        <v>1416</v>
       </c>
       <c r="I181" s="5" t="s">
-        <v>1049</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="182" spans="1:9" ht="87.5" customHeight="1">
       <c r="A182" s="2" t="s">
-        <v>1317</v>
+        <v>1309</v>
       </c>
       <c r="B182" s="2">
         <v>2</v>
       </c>
       <c r="C182" s="15" t="s">
-        <v>1319</v>
+        <v>1311</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>1318</v>
+        <v>1310</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G182" s="5" t="s">
-        <v>1359</v>
+        <v>1351</v>
       </c>
       <c r="H182" s="5" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="183" spans="1:9" ht="92.5" customHeight="1">
       <c r="A183" s="2" t="s">
-        <v>1323</v>
+        <v>1315</v>
       </c>
       <c r="B183" s="2">
         <v>1</v>
       </c>
       <c r="C183" s="15" t="s">
-        <v>1321</v>
+        <v>1313</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="G183" s="5" t="s">
-        <v>1351</v>
+        <v>1343</v>
       </c>
       <c r="H183" s="5" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="91.5" customHeight="1">
       <c r="A184" s="2" t="s">
-        <v>1322</v>
+        <v>1314</v>
       </c>
       <c r="B184" s="2">
         <v>2</v>
       </c>
       <c r="C184" s="15" t="s">
-        <v>1326</v>
+        <v>1318</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>1425</v>
+        <v>1417</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>1324</v>
+        <v>1316</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>1426</v>
+        <v>1418</v>
       </c>
       <c r="H184" s="5" t="s">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="185" spans="1:9" ht="84" customHeight="1">
       <c r="A185" s="2" t="s">
-        <v>1331</v>
+        <v>1323</v>
       </c>
       <c r="B185" s="2">
         <v>1</v>
       </c>
       <c r="C185" s="15" t="s">
-        <v>1328</v>
+        <v>1320</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>1427</v>
+        <v>1419</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>1324</v>
+        <v>1316</v>
       </c>
       <c r="G185" s="5" t="s">
-        <v>1428</v>
+        <v>1420</v>
       </c>
       <c r="H185" s="5" t="s">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="71.5" customHeight="1">
       <c r="A186" s="2" t="s">
-        <v>1327</v>
+        <v>1319</v>
       </c>
       <c r="B186" s="2">
         <v>2</v>
       </c>
       <c r="C186" s="15" t="s">
-        <v>1330</v>
+        <v>1322</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>1329</v>
+        <v>1321</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>1324</v>
+        <v>1316</v>
       </c>
       <c r="G186" s="5" t="s">
-        <v>1353</v>
+        <v>1345</v>
       </c>
       <c r="H186" s="5" t="s">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="77" customHeight="1">
       <c r="A187" s="2" t="s">
-        <v>1332</v>
+        <v>1324</v>
       </c>
       <c r="B187" s="2">
         <v>1</v>
       </c>
       <c r="C187" s="15" t="s">
-        <v>1334</v>
+        <v>1326</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>1333</v>
+        <v>1325</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="G187" s="5" t="s">
-        <v>1354</v>
+        <v>1346</v>
       </c>
       <c r="H187" s="5" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="188" spans="1:9" ht="103.5" customHeight="1">
       <c r="A188" s="2" t="s">
-        <v>1335</v>
+        <v>1327</v>
       </c>
       <c r="B188" s="2">
         <v>2</v>
       </c>
       <c r="C188" s="15" t="s">
-        <v>1336</v>
+        <v>1328</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>1325</v>
+        <v>1317</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G188" s="5" t="s">
-        <v>1352</v>
+        <v>1344</v>
       </c>
       <c r="H188" s="5" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="189" spans="1:9" ht="103.5" customHeight="1">
       <c r="A189" s="2" t="s">
-        <v>1337</v>
+        <v>1329</v>
       </c>
       <c r="B189" s="2">
         <v>1</v>
       </c>
       <c r="C189" s="15" t="s">
-        <v>1339</v>
+        <v>1331</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>1324</v>
+        <v>1316</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>1355</v>
+        <v>1347</v>
       </c>
       <c r="H189" s="5" t="s">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="190" spans="1:9" ht="103.5" customHeight="1">
       <c r="A190" s="2" t="s">
-        <v>1340</v>
+        <v>1332</v>
       </c>
       <c r="B190" s="2">
         <v>1</v>
       </c>
       <c r="C190" s="15" t="s">
-        <v>1341</v>
+        <v>1333</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>1429</v>
+        <v>1421</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>1324</v>
+        <v>1316</v>
       </c>
       <c r="G190" s="5" t="s">
-        <v>1430</v>
+        <v>1422</v>
       </c>
       <c r="H190" s="5" t="s">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="191" spans="1:9" ht="103.5" customHeight="1">
       <c r="A191" s="2" t="s">
-        <v>1345</v>
+        <v>1337</v>
       </c>
       <c r="B191" s="2">
         <v>2</v>
       </c>
       <c r="C191" s="15" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>1338</v>
+      </c>
+      <c r="F191" s="3" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G191" s="5" t="s">
         <v>1348</v>
       </c>
-      <c r="E191" s="3" t="s">
-        <v>1346</v>
-      </c>
-      <c r="F191" s="3" t="s">
-        <v>1324</v>
-      </c>
-      <c r="G191" s="5" t="s">
-        <v>1356</v>
-      </c>
       <c r="H191" s="5" t="s">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="192" spans="1:9" ht="103.5" customHeight="1">
       <c r="A192" s="2" t="s">
-        <v>1344</v>
+        <v>1336</v>
       </c>
       <c r="B192" s="2">
         <v>3</v>
       </c>
       <c r="C192" s="15" t="s">
+        <v>1341</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="G192" s="5" t="s">
         <v>1349</v>
-      </c>
-      <c r="E192" s="3" t="s">
-        <v>1347</v>
-      </c>
-      <c r="G192" s="5" t="s">
-        <v>1357</v>
       </c>
     </row>
     <row r="193" spans="1:9" ht="103.5" customHeight="1">
       <c r="A193" s="2" t="s">
-        <v>1342</v>
+        <v>1334</v>
       </c>
       <c r="B193" s="2">
         <v>2</v>
       </c>
       <c r="C193" s="15" t="s">
-        <v>1343</v>
+        <v>1335</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>1350</v>
+        <v>1342</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G193" s="5" t="s">
-        <v>1358</v>
+        <v>1350</v>
       </c>
       <c r="H193" s="5" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="194" spans="1:9" ht="103.5" customHeight="1">
       <c r="A194" s="2" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B194" s="2">
         <v>0</v>
       </c>
       <c r="C194" s="15" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="D194" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G194" s="5" t="s">
+        <v>1449</v>
+      </c>
+      <c r="H194" s="5" t="s">
+        <v>1450</v>
+      </c>
+      <c r="I194" s="5" t="s">
         <v>1451</v>
-      </c>
-      <c r="E194" s="3" t="s">
-        <v>1445</v>
-      </c>
-      <c r="F194" s="3" t="s">
-        <v>1014</v>
-      </c>
-      <c r="G194" s="5" t="s">
-        <v>1457</v>
-      </c>
-      <c r="H194" s="5" t="s">
-        <v>1458</v>
-      </c>
-      <c r="I194" s="5" t="s">
-        <v>1459</v>
       </c>
     </row>
     <row r="195" spans="1:9" ht="88" customHeight="1">
       <c r="A195" s="2" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="B195" s="2">
         <v>1</v>
       </c>
       <c r="C195" s="15" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>1444</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>1440</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G195" s="5" t="s">
+        <v>1452</v>
+      </c>
+      <c r="H195" s="5" t="s">
         <v>1450</v>
       </c>
-      <c r="D195" s="3" t="s">
-        <v>1452</v>
-      </c>
-      <c r="E195" s="3" t="s">
-        <v>1448</v>
-      </c>
-      <c r="F195" s="3" t="s">
-        <v>1014</v>
-      </c>
-      <c r="G195" s="5" t="s">
-        <v>1460</v>
-      </c>
-      <c r="H195" s="5" t="s">
-        <v>1458</v>
-      </c>
       <c r="I195" s="5" t="s">
-        <v>1461</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="196" spans="1:9" ht="64" customHeight="1">
       <c r="A196" s="2" t="s">
-        <v>1454</v>
+        <v>1446</v>
       </c>
       <c r="B196" s="2">
         <v>0</v>
       </c>
       <c r="C196" s="15" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>1456</v>
+        <v>1448</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>1455</v>
+        <v>1447</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
       <c r="G196" s="5" t="s">
-        <v>1462</v>
+        <v>1454</v>
       </c>
       <c r="H196" s="5" t="s">
-        <v>1458</v>
+        <v>1450</v>
       </c>
     </row>
   </sheetData>
@@ -11806,24 +11737,24 @@
   <sheetData>
     <row r="1" spans="1:5" s="13" customFormat="1" ht="54" customHeight="1">
       <c r="A1" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="C1" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="D1" s="13" t="s">
-        <v>273</v>
-      </c>
       <c r="E1" s="13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="5" customFormat="1" ht="71" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B2" s="5">
         <v>5</v>
@@ -11832,12 +11763,12 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="54" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B3" s="6">
         <v>5</v>
@@ -11846,15 +11777,15 @@
         <v>1</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>930</v>
+        <v>923</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="54" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B4" s="6">
         <v>5</v>
@@ -11863,15 +11794,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>931</v>
+        <v>924</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="54" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B5" s="6">
         <v>10</v>
@@ -11880,12 +11811,12 @@
         <v>2</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="54" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B6" s="6">
         <v>10</v>
@@ -11894,12 +11825,12 @@
         <v>2</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="54" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B7" s="6">
         <v>10</v>
@@ -11908,12 +11839,12 @@
         <v>2</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="41.5" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B8" s="6">
         <v>20</v>
@@ -11922,15 +11853,15 @@
         <v>1</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="41.5" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B9" s="6">
         <v>20</v>
@@ -11939,12 +11870,12 @@
         <v>1</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="41.5" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B10" s="6">
         <v>20</v>
@@ -11953,15 +11884,15 @@
         <v>1</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>928</v>
+        <v>921</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="41.5" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B11" s="6">
         <v>40</v>
@@ -11970,12 +11901,12 @@
         <v>3</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="41.5" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B12" s="6">
         <v>40</v>
@@ -11984,12 +11915,12 @@
         <v>3</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="41.5" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B13" s="6">
         <v>40</v>
@@ -11998,12 +11929,12 @@
         <v>3</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="54" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B14" s="6">
         <v>50</v>
@@ -12012,15 +11943,15 @@
         <v>2</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>934</v>
+        <v>927</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>935</v>
+        <v>928</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="54" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B15" s="6">
         <v>50</v>
@@ -12029,15 +11960,15 @@
         <v>2</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1084</v>
+        <v>1076</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>932</v>
+        <v>925</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="54" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B16" s="6">
         <v>50</v>
@@ -12046,15 +11977,15 @@
         <v>2</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1079</v>
+        <v>1071</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>936</v>
+        <v>929</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="54" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B17" s="6">
         <v>60</v>
@@ -12063,15 +11994,15 @@
         <v>1</v>
       </c>
       <c r="D17" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>323</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="54" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B18" s="6">
         <v>60</v>
@@ -12080,12 +12011,12 @@
         <v>1</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1463</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="54" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B19" s="6">
         <v>60</v>
@@ -12094,15 +12025,15 @@
         <v>1</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1464</v>
+        <v>1456</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="54" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B20" s="6">
         <v>70</v>
@@ -12111,15 +12042,15 @@
         <v>2</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1442</v>
+        <v>1434</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>1441</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="54" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B21" s="6">
         <v>70</v>
@@ -12128,15 +12059,15 @@
         <v>2</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1085</v>
+        <v>1077</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>1086</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="54" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B22" s="6">
         <v>70</v>
@@ -12145,12 +12076,12 @@
         <v>2</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>933</v>
+        <v>926</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="54" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B23" s="6">
         <v>80</v>
@@ -12159,12 +12090,12 @@
         <v>3</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>1434</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="54" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B24" s="6">
         <v>80</v>
@@ -12173,12 +12104,12 @@
         <v>3</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1435</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="54" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B25" s="6">
         <v>80</v>
@@ -12187,12 +12118,12 @@
         <v>3</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="54" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>1439</v>
+        <v>1431</v>
       </c>
       <c r="B26" s="6">
         <v>90</v>
@@ -12201,12 +12132,12 @@
         <v>2</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>1438</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="54" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>1440</v>
+        <v>1432</v>
       </c>
       <c r="B27" s="6">
         <v>90</v>
@@ -12215,12 +12146,12 @@
         <v>2</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>1475</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="54" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B28" s="6">
         <v>90</v>
@@ -12229,12 +12160,12 @@
         <v>2</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>1476</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="54" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B29" s="6">
         <v>100</v>
@@ -12243,15 +12174,15 @@
         <v>3</v>
       </c>
       <c r="D29" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>785</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="156.5" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="B30" s="6">
         <v>100</v>
@@ -12260,15 +12191,15 @@
         <v>3</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>1431</v>
+        <v>1423</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="54" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="B31" s="6">
         <v>100</v>
@@ -12277,15 +12208,15 @@
         <v>3</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>929</v>
+        <v>922</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="76.5" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B32" s="6">
         <v>110</v>
@@ -12294,12 +12225,12 @@
         <v>1</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="54" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B33" s="6">
         <v>110</v>
@@ -12308,12 +12239,12 @@
         <v>1</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>1481</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="54" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B34" s="6">
         <v>110</v>
@@ -12322,12 +12253,12 @@
         <v>1</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="54" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
       <c r="B35" s="6">
         <v>120</v>
@@ -12336,12 +12267,12 @@
         <v>3</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>1102</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="54" customHeight="1">
       <c r="A36" s="6" t="s">
-        <v>1101</v>
+        <v>1093</v>
       </c>
       <c r="B36" s="6">
         <v>120</v>
@@ -12350,7 +12281,7 @@
         <v>3</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>1103</v>
+        <v>1095</v>
       </c>
     </row>
   </sheetData>
@@ -12361,7 +12292,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8EF008-B631-417E-BBAE-17ED938F4B44}">
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr defaultColWidth="15.33203125" defaultRowHeight="55" customHeight="1"/>
   <cols>
     <col min="1" max="16384" width="15.33203125" style="6"/>
@@ -12386,120 +12317,120 @@
     </row>
     <row r="2" spans="1:5" ht="55" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="B2" s="6">
         <v>1</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="55" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="B3" s="6">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>924</v>
+        <v>917</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="55" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B4" s="6">
         <v>1</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>923</v>
+        <v>916</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="55" customHeight="1" thickBot="1">
       <c r="A5" s="6" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="B5" s="6">
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>922</v>
+        <v>915</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="55" customHeight="1" thickBot="1">
       <c r="A6" s="16" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="B6" s="8">
         <v>2</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="9" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="55" customHeight="1" thickBot="1">
       <c r="A7" s="16" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="B7" s="8">
         <v>2</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="9" t="s">
-        <v>920</v>
+        <v>913</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="55" customHeight="1" thickBot="1">
       <c r="A8" s="11" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="B8" s="8">
         <v>3</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="9" t="s">
-        <v>919</v>
+        <v>912</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="55" customHeight="1" thickBot="1">
       <c r="A9" s="11" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="B9" s="8">
         <v>3</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="D9" s="8">
         <v>1</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="55" customHeight="1">
@@ -12518,66 +12449,66 @@
     </row>
     <row r="11" spans="1:5" ht="55" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B11" s="6">
         <v>2</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="55" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B12" s="6">
         <v>2</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="55" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
       <c r="B13" s="6">
         <v>3</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="55" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>1082</v>
+        <v>1074</v>
       </c>
       <c r="B14" s="6">
         <v>3</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1080</v>
+        <v>1072</v>
       </c>
       <c r="D14" s="6">
         <v>1</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>1081</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="55" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>942</v>
+        <v>935</v>
       </c>
       <c r="B15" s="6">
         <v>1</v>
@@ -12591,13 +12522,13 @@
     </row>
     <row r="16" spans="1:5" ht="55" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>941</v>
+        <v>934</v>
       </c>
       <c r="B16" s="6">
         <v>2</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>938</v>
+        <v>931</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>142</v>
@@ -12605,16 +12536,16 @@
     </row>
     <row r="17" spans="1:5" ht="55" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>937</v>
+        <v>930</v>
       </c>
       <c r="B17" s="6">
         <v>3</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>939</v>
+        <v>932</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>940</v>
+        <v>933</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="55" customHeight="1">
@@ -12678,7 +12609,7 @@
     </row>
     <row r="22" spans="1:5" ht="55" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B22" s="6">
         <v>2</v>
@@ -12706,7 +12637,7 @@
     </row>
     <row r="24" spans="1:5" ht="55" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B24" s="6">
         <v>2</v>
@@ -12779,7 +12710,7 @@
     </row>
     <row r="29" spans="1:5" ht="55" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B29" s="6">
         <v>3</v>
@@ -12802,10 +12733,10 @@
         <v>1</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="55" customHeight="1">
@@ -12816,24 +12747,24 @@
         <v>2</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="55" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B32" s="6">
         <v>3</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="55" customHeight="1">
@@ -12844,7 +12775,7 @@
         <v>3</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="D33" s="6">
         <v>1</v>
@@ -12892,157 +12823,157 @@
         <v>185</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="55" customHeight="1">
       <c r="A37" s="6" t="s">
-        <v>1316</v>
+        <v>1308</v>
       </c>
       <c r="B37" s="6">
         <v>2</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>1302</v>
+        <v>1294</v>
       </c>
       <c r="D37" s="6">
         <v>1</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>1305</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="55" customHeight="1">
       <c r="A38" s="6" t="s">
-        <v>1315</v>
+        <v>1307</v>
       </c>
       <c r="B38" s="6">
         <v>2</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>1303</v>
+        <v>1295</v>
       </c>
       <c r="D38" s="6">
         <v>1</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>1304</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="55" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B39" s="6">
         <v>2</v>
       </c>
       <c r="C39" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="D39" s="6">
+        <v>1</v>
+      </c>
+      <c r="E39" s="6" t="s">
         <v>483</v>
-      </c>
-      <c r="D39" s="6">
-        <v>1</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="55" customHeight="1">
       <c r="A40" s="6" t="s">
-        <v>1244</v>
+        <v>1236</v>
       </c>
       <c r="B40" s="6">
         <v>2</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>1245</v>
+        <v>1237</v>
       </c>
       <c r="D40" s="6">
         <v>1</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>1246</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="55" customHeight="1">
       <c r="A41" s="6" t="s">
-        <v>1255</v>
+        <v>1247</v>
       </c>
       <c r="B41" s="6">
         <v>3</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>1247</v>
+        <v>1239</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>1248</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="55" customHeight="1">
       <c r="A42" s="6" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B42" s="6">
         <v>2</v>
       </c>
       <c r="C42" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>644</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="55" customHeight="1">
       <c r="A43" s="6" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B43" s="6">
         <v>2</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D43" s="6">
         <v>1</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>948</v>
+        <v>941</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="55" customHeight="1">
       <c r="A44" s="6" t="s">
-        <v>1044</v>
+        <v>1037</v>
       </c>
       <c r="B44" s="6">
         <v>3</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>1046</v>
+        <v>1039</v>
       </c>
       <c r="D44" s="6">
         <v>1</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>1047</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="55" customHeight="1">
       <c r="A45" s="6" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B45" s="6">
         <v>3</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>1045</v>
+        <v>1038</v>
       </c>
       <c r="D45" s="6">
         <v>1</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>1048</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="55" customHeight="1">
@@ -13061,7 +12992,7 @@
     </row>
     <row r="47" spans="1:5" ht="55" customHeight="1">
       <c r="A47" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B47" s="6">
         <v>1</v>
@@ -13089,44 +13020,44 @@
     </row>
     <row r="49" spans="1:5" ht="55" customHeight="1">
       <c r="A49" s="6" t="s">
-        <v>1254</v>
+        <v>1246</v>
       </c>
       <c r="B49" s="6">
         <v>2</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>1252</v>
+        <v>1244</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="55" customHeight="1">
       <c r="A50" s="6" t="s">
-        <v>1251</v>
+        <v>1243</v>
       </c>
       <c r="B50" s="6">
         <v>1</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>1249</v>
+        <v>1241</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>1250</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="55" customHeight="1">
       <c r="A51" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B51" s="6">
         <v>1</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="55" customHeight="1">
@@ -13151,27 +13082,27 @@
         <v>1</v>
       </c>
       <c r="C53" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>634</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="55" customHeight="1">
       <c r="A54" s="6" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="B54" s="6">
         <v>3</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="D54" s="6">
         <v>1</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="55" customHeight="1">
@@ -13196,7 +13127,7 @@
         <v>1</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>202</v>
@@ -13210,10 +13141,10 @@
         <v>1</v>
       </c>
       <c r="C57" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="E57" s="6" t="s">
         <v>641</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="55" customHeight="1">
@@ -13232,19 +13163,19 @@
     </row>
     <row r="59" spans="1:5" ht="55" customHeight="1">
       <c r="A59" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B59" s="6">
         <v>2</v>
       </c>
       <c r="C59" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="D59" s="6">
+        <v>1</v>
+      </c>
+      <c r="E59" s="6" t="s">
         <v>444</v>
-      </c>
-      <c r="D59" s="6">
-        <v>1</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="55" customHeight="1">
@@ -13255,7 +13186,7 @@
         <v>1</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D60" s="6">
         <v>1</v>
@@ -13317,19 +13248,19 @@
     </row>
     <row r="64" spans="1:5" ht="55" customHeight="1">
       <c r="A64" s="6" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B64" s="6">
         <v>1</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D64" s="6">
         <v>1</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="55" customHeight="1">
@@ -13340,7 +13271,7 @@
         <v>1</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D65" s="6">
         <v>1</v>
@@ -13357,13 +13288,13 @@
         <v>1</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D66" s="6">
         <v>1</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="55" customHeight="1">
@@ -13374,7 +13305,7 @@
         <v>3</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D67" s="6">
         <v>1</v>
@@ -13385,19 +13316,19 @@
     </row>
     <row r="68" spans="1:5" ht="55" customHeight="1">
       <c r="A68" s="6" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B68" s="6">
         <v>1</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D68" s="6">
         <v>1</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="60" customHeight="1">
@@ -13408,7 +13339,7 @@
         <v>3</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D69" s="6">
         <v>1</v>
@@ -13425,7 +13356,7 @@
         <v>1</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
       <c r="D70" s="6">
         <v>1</v>
@@ -13442,7 +13373,7 @@
         <v>3</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>1157</v>
+        <v>1149</v>
       </c>
       <c r="D71" s="6">
         <v>1</v>
@@ -13453,24 +13384,24 @@
     </row>
     <row r="72" spans="1:5" ht="55" customHeight="1">
       <c r="A72" s="6" t="s">
-        <v>1159</v>
+        <v>1151</v>
       </c>
       <c r="B72" s="6">
         <v>2</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>1158</v>
+        <v>1150</v>
       </c>
       <c r="D72" s="6">
         <v>1</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>1160</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="55" customHeight="1">
       <c r="A73" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B73" s="6">
         <v>3</v>
@@ -13543,19 +13474,19 @@
     </row>
     <row r="78" spans="1:5" ht="55" customHeight="1">
       <c r="A78" s="6" t="s">
-        <v>947</v>
+        <v>940</v>
       </c>
       <c r="B78" s="6">
         <v>3</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>1479</v>
+        <v>1471</v>
       </c>
       <c r="D78" s="6">
         <v>1</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>1480</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="55" customHeight="1">
@@ -13616,801 +13547,761 @@
     </row>
     <row r="83" spans="1:5" ht="55" customHeight="1" thickBot="1">
       <c r="A83" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B83" s="6">
         <v>3</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D83" s="6">
         <v>1</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="55" customHeight="1" thickBot="1">
       <c r="A84" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B84" s="8">
         <v>1</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D84" s="8"/>
       <c r="E84" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="55" customHeight="1" thickBot="1">
       <c r="A85" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B85" s="8">
         <v>1</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D85" s="8"/>
       <c r="E85" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="55" customHeight="1" thickBot="1">
       <c r="A86" s="11" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B86" s="8">
         <v>2</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D86" s="8"/>
       <c r="E86" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="55" customHeight="1" thickBot="1">
       <c r="A87" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B87" s="8">
         <v>3</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D87" s="8"/>
       <c r="E87" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="55" customHeight="1" thickBot="1">
       <c r="A88" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B88" s="8">
         <v>3</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D88" s="8">
         <v>1</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="55" customHeight="1" thickBot="1">
       <c r="A89" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B89" s="8">
+        <v>1</v>
+      </c>
+      <c r="C89" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="B89" s="8">
-        <v>1</v>
-      </c>
-      <c r="C89" s="10" t="s">
-        <v>266</v>
-      </c>
       <c r="D89" s="8">
         <v>1</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="55" customHeight="1">
       <c r="A90" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B90" s="6">
         <v>2</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="54" customHeight="1">
       <c r="A91" s="6" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
       <c r="B91" s="6">
         <v>3</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>1068</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="54" customHeight="1">
       <c r="A92" s="6" t="s">
-        <v>1069</v>
+        <v>1061</v>
       </c>
       <c r="B92" s="6">
         <v>2</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>1067</v>
+        <v>1059</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>1065</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="54" customHeight="1">
       <c r="A93" s="6" t="s">
-        <v>1306</v>
+        <v>1298</v>
       </c>
       <c r="B93" s="6">
         <v>1</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>1307</v>
+        <v>1299</v>
       </c>
       <c r="D93" s="6">
         <v>1</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>1308</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="55" customHeight="1">
       <c r="A94" s="6" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="B94" s="6">
         <v>1</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="55" customHeight="1">
       <c r="A95" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="B95" s="6">
+        <v>1</v>
+      </c>
+      <c r="C95" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="B95" s="6">
-        <v>1</v>
-      </c>
-      <c r="C95" s="6" t="s">
+      <c r="E95" s="6" t="s">
         <v>332</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="55" customHeight="1">
       <c r="A96" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="B96" s="6">
         <v>1</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="55" customHeight="1">
       <c r="A97" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B97" s="6">
         <v>1</v>
       </c>
       <c r="C97" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="E97" s="6" t="s">
         <v>485</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="55" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B98" s="6">
         <v>2</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="55" customHeight="1">
       <c r="A99" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B99" s="6">
         <v>3</v>
       </c>
       <c r="C99" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="D99" s="6">
+        <v>1</v>
+      </c>
+      <c r="E99" s="6" t="s">
         <v>447</v>
-      </c>
-      <c r="D99" s="6">
-        <v>1</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="55" customHeight="1">
       <c r="A100" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B100" s="6">
         <v>1</v>
       </c>
       <c r="C100" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="E100" s="6" t="s">
         <v>506</v>
-      </c>
-      <c r="E100" s="6" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="55" customHeight="1">
       <c r="A101" s="6" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B101" s="6">
         <v>1</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="55" customHeight="1">
       <c r="A102" s="6" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B102" s="6">
         <v>1</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="55" customHeight="1">
       <c r="A103" s="6" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B103" s="6">
         <v>2</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="55" customHeight="1">
       <c r="A104" s="6" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B104" s="6">
         <v>3</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="55" customHeight="1">
       <c r="A105" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="B105" s="6">
+        <v>1</v>
+      </c>
+      <c r="C105" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="B105" s="6">
-        <v>1</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>633</v>
-      </c>
       <c r="E105" s="6" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="55" customHeight="1">
       <c r="A106" s="6" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B106" s="6">
         <v>1</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D106" s="6">
         <v>1</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="55" customHeight="1">
       <c r="A107" s="6" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B107" s="6">
         <v>2</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D107" s="6">
         <v>1</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="55" customHeight="1">
       <c r="A108" s="6" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B108" s="6">
         <v>3</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="D108" s="6">
         <v>1</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="55" customHeight="1">
       <c r="A109" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B109" s="6">
         <v>3</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D109" s="6">
         <v>1</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="55" customHeight="1">
       <c r="A110" s="6" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B110" s="6">
         <v>1</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="D110" s="6">
         <v>1</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="55" customHeight="1">
       <c r="A111" s="6" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B111" s="6">
         <v>1</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="55" customHeight="1">
       <c r="A112" s="6" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B112" s="6">
         <v>2</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="55" customHeight="1">
       <c r="A113" s="6" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B113" s="6">
         <v>1</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="55" customHeight="1">
       <c r="A114" s="6" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="B114" s="6">
         <v>2</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" ht="55" customHeight="1" thickBot="1">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="55" customHeight="1">
       <c r="A115" s="6" t="s">
-        <v>1165</v>
+        <v>1157</v>
       </c>
       <c r="B115" s="6">
         <v>3</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>1163</v>
+        <v>1155</v>
       </c>
       <c r="D115" s="6">
         <v>1</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" ht="55" customHeight="1" thickBot="1">
-      <c r="A116" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="B116" s="8">
-        <v>1</v>
-      </c>
-      <c r="C116" s="10" t="s">
-        <v>904</v>
-      </c>
-      <c r="D116" s="8"/>
-      <c r="E116" s="9" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" ht="65" customHeight="1">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="65" customHeight="1">
+      <c r="A116" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="B116" s="6">
+        <v>3</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>937</v>
+      </c>
+      <c r="D116" s="6">
+        <v>1</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="55" customHeight="1">
       <c r="A117" s="6" t="s">
-        <v>717</v>
+        <v>771</v>
       </c>
       <c r="B117" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>944</v>
+        <v>772</v>
       </c>
       <c r="D117" s="6">
         <v>1</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>945</v>
+        <v>776</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="55" customHeight="1">
       <c r="A118" s="6" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="B118" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D118" s="6">
         <v>1</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="55" customHeight="1">
       <c r="A119" s="6" t="s">
-        <v>783</v>
+        <v>887</v>
       </c>
       <c r="B119" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>781</v>
-      </c>
-      <c r="D119" s="6">
-        <v>1</v>
+        <v>888</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>782</v>
+        <v>889</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="55" customHeight="1">
       <c r="A120" s="6" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="B120" s="6">
         <v>1</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>893</v>
+        <v>918</v>
+      </c>
+      <c r="D120" s="6">
+        <v>1</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="55" customHeight="1">
       <c r="A121" s="6" t="s">
-        <v>906</v>
+        <v>1043</v>
       </c>
       <c r="B121" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>925</v>
+        <v>1044</v>
       </c>
       <c r="D121" s="6">
         <v>1</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>908</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="55" customHeight="1">
       <c r="A122" s="6" t="s">
-        <v>1050</v>
+        <v>660</v>
       </c>
       <c r="B122" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>1051</v>
-      </c>
-      <c r="D122" s="6">
-        <v>1</v>
+        <v>1046</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="55" customHeight="1">
       <c r="A123" s="6" t="s">
-        <v>662</v>
+        <v>1050</v>
       </c>
       <c r="B123" s="6">
         <v>1</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>1053</v>
+        <v>1048</v>
+      </c>
+      <c r="D123" s="6">
+        <v>1</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="55" customHeight="1">
       <c r="A124" s="6" t="s">
-        <v>1058</v>
+        <v>1067</v>
       </c>
       <c r="B124" s="6">
         <v>1</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
       <c r="D124" s="6">
         <v>1</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>1059</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="55" customHeight="1">
       <c r="A125" s="6" t="s">
-        <v>1075</v>
+        <v>1066</v>
       </c>
       <c r="B125" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="D125" s="6">
         <v>1</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="55" customHeight="1">
       <c r="A126" s="6" t="s">
-        <v>1074</v>
+        <v>1065</v>
       </c>
       <c r="B126" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>1072</v>
+        <v>1062</v>
       </c>
       <c r="D126" s="6">
         <v>1</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>1078</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="55" customHeight="1">
       <c r="A127" s="6" t="s">
-        <v>1073</v>
+        <v>1112</v>
       </c>
       <c r="B127" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>1070</v>
+        <v>1110</v>
       </c>
       <c r="D127" s="6">
         <v>1</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>1077</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="55" customHeight="1">
       <c r="A128" s="6" t="s">
-        <v>1120</v>
+        <v>1108</v>
       </c>
       <c r="B128" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>1118</v>
+        <v>1103</v>
       </c>
       <c r="D128" s="6">
         <v>1</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>1119</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="55" customHeight="1">
       <c r="A129" s="6" t="s">
-        <v>1116</v>
+        <v>1109</v>
       </c>
       <c r="B129" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>1111</v>
+        <v>1104</v>
       </c>
       <c r="D129" s="6">
         <v>1</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>1114</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="55" customHeight="1">
       <c r="A130" s="6" t="s">
-        <v>1117</v>
+        <v>659</v>
       </c>
       <c r="B130" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D130" s="6">
-        <v>1</v>
+        <v>1353</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>1115</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="55" customHeight="1">
       <c r="A131" s="6" t="s">
-        <v>660</v>
+        <v>1475</v>
       </c>
       <c r="B131" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>1361</v>
-      </c>
-      <c r="E131" s="6" t="s">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" ht="55" customHeight="1">
-      <c r="A132" s="6" t="s">
-        <v>1483</v>
-      </c>
-      <c r="B132" s="6">
-        <v>3</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>1482</v>
-      </c>
-      <c r="D132" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" ht="55" customHeight="1">
-      <c r="A134" s="6" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" ht="55" customHeight="1">
-      <c r="A135" s="6" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" ht="55" customHeight="1">
-      <c r="A136" s="6" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" ht="55" customHeight="1">
-      <c r="A137" s="6" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" ht="55" customHeight="1">
-      <c r="A138" s="6" t="s">
-        <v>1057</v>
+        <v>1474</v>
+      </c>
+      <c r="D131" s="6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
